--- a/final_output_LOOCV1.xlsx
+++ b/final_output_LOOCV1.xlsx
@@ -1,20 +1,26 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <fileVersion appName="xl" lastEdited="4" lowestEdited="4" rupBuild="4505"/>
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="4" rupBuild="11208"/>
   <workbookPr defaultThemeVersion="124226"/>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice Requires="x15">
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/macbookpro/Desktop/合金设计新方法/高温合金微观组织模型/微观组织预测/"/>
+    </mc:Choice>
+  </mc:AlternateContent>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{CE74F5FA-6154-4249-87E8-60B4E39218F7}" xr6:coauthVersionLast="45" xr6:coauthVersionMax="45" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="240" yWindow="15" windowWidth="16095" windowHeight="9660"/>
+    <workbookView xWindow="0" yWindow="0" windowWidth="38400" windowHeight="21600" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
   </sheets>
-  <calcPr calcId="124519" fullCalcOnLoad="1"/>
+  <calcPr calcId="124519"/>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="7" uniqueCount="7">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="11" uniqueCount="11">
   <si>
     <t>MAPE</t>
   </si>
@@ -28,24 +34,39 @@
     <t>R2</t>
   </si>
   <si>
-    <t>UTS</t>
-  </si>
-  <si>
-    <t>TYS</t>
-  </si>
-  <si>
-    <t xml:space="preserve"> Elong</t>
+    <t>基体相体积分数</t>
+  </si>
+  <si>
+    <t>强化相体积分数</t>
+  </si>
+  <si>
+    <t xml:space="preserve"> 液相温度</t>
+  </si>
+  <si>
+    <t>固相温度</t>
+  </si>
+  <si>
+    <t>凝固区间</t>
+  </si>
+  <si>
+    <t>强化相溶解温度</t>
+  </si>
+  <si>
+    <t>加工窗口</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
-<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <fonts count="2">
+<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
+  <numFmts count="1">
+    <numFmt numFmtId="176" formatCode="0.00_ "/>
+  </numFmts>
+  <fonts count="3">
     <font>
       <sz val="11"/>
       <color theme="1"/>
-      <name val="Calibri"/>
+      <name val="宋体"/>
       <family val="2"/>
       <scheme val="minor"/>
     </font>
@@ -53,8 +74,15 @@
       <b/>
       <sz val="11"/>
       <color theme="1"/>
-      <name val="Calibri"/>
+      <name val="宋体"/>
       <family val="2"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="9"/>
+      <name val="宋体"/>
+      <family val="3"/>
+      <charset val="134"/>
       <scheme val="minor"/>
     </font>
   </fonts>
@@ -93,22 +121,33 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="2">
+  <cellXfs count="3">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="top"/>
+    <xf numFmtId="176" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="176" fontId="1" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
-    <cellStyle name="Normal" xfId="0" builtinId="0"/>
+    <cellStyle name="常规" xfId="0" builtinId="0"/>
   </cellStyles>
   <dxfs count="0"/>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium9" defaultPivotStyle="PivotStyleLight16"/>
+  <extLst>
+    <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{EB79DEF2-80B8-43e5-95BD-54CBDDF9020C}">
+      <x14:slicerStyles defaultSlicerStyle="SlicerStyleLight1"/>
+    </ext>
+    <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{9260A510-F301-46a8-8635-F512D64BE5F5}">
+      <x15:timelineStyles defaultTimelineStyle="TimeSlicerStyleLight1"/>
+    </ext>
+  </extLst>
 </styleSheet>
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
-<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Office Theme">
+<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Office 主题​​">
   <a:themeElements>
     <a:clrScheme name="Office">
       <a:dk1>
@@ -150,7 +189,7 @@
     </a:clrScheme>
     <a:fontScheme name="Office">
       <a:majorFont>
-        <a:latin typeface="Cambria"/>
+        <a:latin typeface="Cambria" panose="020F0302020204030204"/>
         <a:ea typeface=""/>
         <a:cs typeface=""/>
         <a:font script="Jpan" typeface="ＭＳ Ｐゴシック"/>
@@ -182,9 +221,27 @@
         <a:font script="Mong" typeface="Mongolian Baiti"/>
         <a:font script="Viet" typeface="Times New Roman"/>
         <a:font script="Uigh" typeface="Microsoft Uighur"/>
+        <a:font script="Geor" typeface="Sylfaen"/>
+        <a:font script="Armn" typeface="Arial"/>
+        <a:font script="Bugi" typeface="Leelawadee UI"/>
+        <a:font script="Bopo" typeface="Microsoft JhengHei"/>
+        <a:font script="Java" typeface="Javanese Text"/>
+        <a:font script="Lisu" typeface="Segoe UI"/>
+        <a:font script="Mymr" typeface="Myanmar Text"/>
+        <a:font script="Nkoo" typeface="Ebrima"/>
+        <a:font script="Olck" typeface="Nirmala UI"/>
+        <a:font script="Osma" typeface="Ebrima"/>
+        <a:font script="Phag" typeface="Phagspa"/>
+        <a:font script="Syrn" typeface="Estrangelo Edessa"/>
+        <a:font script="Syrj" typeface="Estrangelo Edessa"/>
+        <a:font script="Syre" typeface="Estrangelo Edessa"/>
+        <a:font script="Sora" typeface="Nirmala UI"/>
+        <a:font script="Tale" typeface="Microsoft Tai Le"/>
+        <a:font script="Talu" typeface="Microsoft New Tai Lue"/>
+        <a:font script="Tfng" typeface="Ebrima"/>
       </a:majorFont>
       <a:minorFont>
-        <a:latin typeface="Calibri"/>
+        <a:latin typeface="Calibri" panose="020F0502020204030204"/>
         <a:ea typeface=""/>
         <a:cs typeface=""/>
         <a:font script="Jpan" typeface="ＭＳ Ｐゴシック"/>
@@ -216,6 +273,24 @@
         <a:font script="Mong" typeface="Mongolian Baiti"/>
         <a:font script="Viet" typeface="Arial"/>
         <a:font script="Uigh" typeface="Microsoft Uighur"/>
+        <a:font script="Geor" typeface="Sylfaen"/>
+        <a:font script="Armn" typeface="Arial"/>
+        <a:font script="Bugi" typeface="Leelawadee UI"/>
+        <a:font script="Bopo" typeface="Microsoft JhengHei"/>
+        <a:font script="Java" typeface="Javanese Text"/>
+        <a:font script="Lisu" typeface="Segoe UI"/>
+        <a:font script="Mymr" typeface="Myanmar Text"/>
+        <a:font script="Nkoo" typeface="Ebrima"/>
+        <a:font script="Olck" typeface="Nirmala UI"/>
+        <a:font script="Osma" typeface="Ebrima"/>
+        <a:font script="Phag" typeface="Phagspa"/>
+        <a:font script="Syrn" typeface="Estrangelo Edessa"/>
+        <a:font script="Syrj" typeface="Estrangelo Edessa"/>
+        <a:font script="Syre" typeface="Estrangelo Edessa"/>
+        <a:font script="Sora" typeface="Nirmala UI"/>
+        <a:font script="Tale" typeface="Microsoft Tai Le"/>
+        <a:font script="Talu" typeface="Microsoft New Tai Lue"/>
+        <a:font script="Tfng" typeface="Ebrima"/>
       </a:minorFont>
     </a:fontScheme>
     <a:fmtScheme name="Office">
@@ -391,76 +466,146 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:E4"/>
-  <sheetFormatPr defaultRowHeight="15"/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
+  <dimension ref="A1:E8"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="14"/>
   <sheetData>
     <row r="1" spans="1:5">
-      <c r="B1" s="1" t="s">
+      <c r="A1" s="1"/>
+      <c r="B1" s="2" t="s">
         <v>0</v>
       </c>
-      <c r="C1" s="1" t="s">
+      <c r="C1" s="2" t="s">
         <v>1</v>
       </c>
-      <c r="D1" s="1" t="s">
+      <c r="D1" s="2" t="s">
         <v>2</v>
       </c>
-      <c r="E1" s="1" t="s">
+      <c r="E1" s="2" t="s">
         <v>3</v>
       </c>
     </row>
     <row r="2" spans="1:5">
-      <c r="A2" s="1" t="s">
+      <c r="A2" s="2" t="s">
         <v>4</v>
       </c>
-      <c r="B2">
-        <v>4.916889213611396</v>
-      </c>
-      <c r="C2">
-        <v>53.61145372909485</v>
-      </c>
-      <c r="D2">
-        <v>89.3294570092819</v>
-      </c>
-      <c r="E2">
-        <v>0.9177864969488368</v>
+      <c r="B2" s="1">
+        <v>2.9517408910964709</v>
+      </c>
+      <c r="C2" s="1">
+        <v>1.899745753086417</v>
+      </c>
+      <c r="D2" s="1">
+        <v>3.3017079848532691</v>
+      </c>
+      <c r="E2" s="1">
+        <v>0.9053267493287992</v>
       </c>
     </row>
     <row r="3" spans="1:5">
-      <c r="A3" s="1" t="s">
+      <c r="A3" s="2" t="s">
         <v>5</v>
       </c>
-      <c r="B3">
-        <v>7.251052754912238</v>
-      </c>
-      <c r="C3">
-        <v>55.69703429656583</v>
-      </c>
-      <c r="D3">
-        <v>89.06037789200208</v>
-      </c>
-      <c r="E3">
-        <v>0.8948071615372182</v>
+      <c r="B3" s="1">
+        <v>6.555674324947816</v>
+      </c>
+      <c r="C3" s="1">
+        <v>0.94827059259259205</v>
+      </c>
+      <c r="D3" s="1">
+        <v>1.632518322907639</v>
+      </c>
+      <c r="E3" s="1">
+        <v>0.98454533997838645</v>
       </c>
     </row>
     <row r="4" spans="1:5">
-      <c r="A4" s="1" t="s">
+      <c r="A4" s="2" t="s">
         <v>6</v>
       </c>
-      <c r="B4">
-        <v>20.41181932709253</v>
-      </c>
-      <c r="C4">
-        <v>4.011637579811907</v>
-      </c>
-      <c r="D4">
-        <v>6.308571923837876</v>
-      </c>
-      <c r="E4">
-        <v>0.800480779852911</v>
+      <c r="B4" s="1">
+        <v>0.2385950299899694</v>
+      </c>
+      <c r="C4" s="1">
+        <v>3.2430403827160208</v>
+      </c>
+      <c r="D4" s="1">
+        <v>6.1987029539399714</v>
+      </c>
+      <c r="E4" s="1">
+        <v>0.80666241466975352</v>
+      </c>
+    </row>
+    <row r="5" spans="1:5">
+      <c r="A5" s="2" t="s">
+        <v>7</v>
+      </c>
+      <c r="B5" s="1">
+        <v>0.59013221987795961</v>
+      </c>
+      <c r="C5" s="1">
+        <v>7.4937903703702968</v>
+      </c>
+      <c r="D5" s="1">
+        <v>12.421010590318749</v>
+      </c>
+      <c r="E5" s="1">
+        <v>0.93228291825352871</v>
+      </c>
+    </row>
+    <row r="6" spans="1:5">
+      <c r="A6" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="B6" s="1">
+        <v>8.0634005367865971</v>
+      </c>
+      <c r="C6" s="1">
+        <v>6.7345017283950588</v>
+      </c>
+      <c r="D6" s="1">
+        <v>11.240164692255339</v>
+      </c>
+      <c r="E6" s="1">
+        <v>0.94228699300139762</v>
+      </c>
+    </row>
+    <row r="7" spans="1:5">
+      <c r="A7" s="2" t="s">
+        <v>9</v>
+      </c>
+      <c r="B7" s="1">
+        <v>0.85307337927483418</v>
+      </c>
+      <c r="C7" s="1">
+        <v>8.2810999259258935</v>
+      </c>
+      <c r="D7" s="1">
+        <v>13.918559065096289</v>
+      </c>
+      <c r="E7" s="1">
+        <v>0.97670632083213094</v>
+      </c>
+    </row>
+    <row r="8" spans="1:5">
+      <c r="A8" s="2" t="s">
+        <v>10</v>
+      </c>
+      <c r="B8" s="1">
+        <v>6.5304629482156136</v>
+      </c>
+      <c r="C8" s="1">
+        <v>16.359827518518522</v>
+      </c>
+      <c r="D8" s="1">
+        <v>23.929717334191089</v>
+      </c>
+      <c r="E8" s="1">
+        <v>0.91125352021386929</v>
       </c>
     </row>
   </sheetData>
+  <phoneticPr fontId="2" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
 </file>